--- a/Documents/jlc_BOM.xlsx
+++ b/Documents/jlc_BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="138">
   <si>
     <t xml:space="preserve">Comment</t>
   </si>
@@ -34,118 +34,388 @@
     <t xml:space="preserve">Quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">PinHeader_1x2_P2mm_Drill1mm_RA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R213,R202,R208,R212,R211,R206,R210,R201,R207,R504,R209,R204,R203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R_0603_1608Metric</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 pF</t>
   </si>
   <si>
     <t xml:space="preserve">C201,C207</t>
   </si>
   <si>
-    <t xml:space="preserve">C_0603_1608Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UART4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UART1</t>
+    <t xml:space="preserve">Capacitor_SMD:C_0603_1608Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C202,C206</t>
   </si>
   <si>
     <t xml:space="preserve">1uF</t>
   </si>
   <si>
-    <t xml:space="preserve">C603,C606,C209,C613,C203,C614,C601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BWSMA-KWE-Z001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J303,J301,J302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF_SMA_RightAngle_5-1814400-1</t>
+    <t xml:space="preserve">C203,C209,C601,C603,C606,C613,C614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C204,C505,C506,C507,C511,C512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor_SMD:C_0805_2012Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C205,C208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C210,C211,C212,C213,C401,C501,C508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C301,C305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C304,C312,C315,C316,C322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C306,C307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C308,C309,C313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C311,C321,C323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C317,C318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C502,C503,C504,C509,C510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D201,D501,D502,D503,D504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED_SMD:LED_0805_2012Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">015402.5DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">015402.5DR:0154Series_LTF</t>
   </si>
   <si>
     <t xml:space="preserve">0154001.DR</t>
   </si>
   <si>
-    <t xml:space="preserve">F503,F502,F504,F505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUSE_0154001.DR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100nF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C213,C401,C501,C211,C508,C210,C212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330R 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R509,R205,R508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PinHeader_1x4_P2.5mm_Drill1.1mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRESSURE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C202,C206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUMIDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TerminalBlock_MaiXu_MX126-5.0-02P_1x02_P5.00mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UART2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1720BL15B0200E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL303,FL302,FL301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D502,D201,D504,D501,D503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LED_0805_2012Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2K 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R402,R401,R403</t>
+    <t xml:space="preserve">F502,F503,F504,F505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0154001.DR:FUSE_0154001.DR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5K 0.5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductor_SMD:L_0603_1608Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8uH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductor_SMD:L_0805_2012Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductor_SMD:L_0402_1005Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L302,L303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L304,L311,L312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L306,L308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L309,L310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L314,L315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L316,L318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9nH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSM84338RCJR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPSM84338RCJR:CONV_TPSM84338RCJR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R201,R202,R203,R204,R206,R207,R208,R209,R210,R211,R212,R213,R504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R205,R508,R509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R401,R402,R403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R601,R611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R602,R603,R607,R608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R604,R606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1354P106T0RGZR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1354P106T0RGZR:VQFN48_RGZ_TEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTC1694CS5TRMPBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTC1694CS5TRMPBF:SOT95P280X100-5N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX25R1635FZUIL0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX25R1635FZUIL0:USON-8L-2X3X0P6_MAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ1117CH2-3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U501,U502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package_TO_SOT_SMD:SOT-223-3_TabPin2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLV9002IDR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLV9002IDR:SOIC127P599X175-8N</t>
   </si>
   <si>
     <t xml:space="preserve">ABM11W-48.0000MHZ-7-B1U-T3</t>
@@ -154,22 +424,7 @@
     <t xml:space="preserve">Y201</t>
   </si>
   <si>
-    <t xml:space="preserve">XTAL_ABM11W-48.0000MHZ-7-B1U-T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5K 0.5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L_0603_1608Metric</t>
+    <t xml:space="preserve">ABM11W-48.0000MHZ-7-B1U-T3:XTAL_ABM11W-48.0000MHZ-7-B1U-T3</t>
   </si>
   <si>
     <t xml:space="preserve">ABS07-32.768KHZ-T</t>
@@ -178,181 +433,7 @@
     <t xml:space="preserve">Y202</t>
   </si>
   <si>
-    <t xml:space="preserve">XTAL_ABS07-32.768KHZ-T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RCT-0C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3V3,3V3 F,5V,Pipe,Amb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROBE_PAD_0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PinHeader_1x06_P2.54mm_Vertical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LTC1694CS5TRMPBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT95P280X100-5N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC1354P106T0RGZR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VQFN48_RGZ_TEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">015402.5DR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0154Series_LTF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C504,C502,C509,C503,C510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C_0805_2012Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UART3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C204,C506,C512,C507,C505,C511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R607,R602,R608,R603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ1117CH2-3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U501,U502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOT-223-3_TabPin2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R606,R604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MX25R1635FZUIL0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USON-8L-2X3X0P6_MAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R611,R601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPSM84338RCJR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONV_TPSM84338RCJR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C208,C205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8uH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L_0805_2012Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2k 0.1% 25ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLV9002IDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOIC127P599X175-8N</t>
+    <t xml:space="preserve">ABS07-32.768KHZ-T:XTAL_ABS07-32.768KHZ-T</t>
   </si>
 </sst>
 </file>
@@ -362,11 +443,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -383,48 +465,21 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC0000"/>
-        <bgColor rgb="FF800000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF808080"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF808080"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF808080"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF808080"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -453,13 +508,9 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -471,66 +522,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFCC0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -539,15 +530,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D59"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.2"/>
   </cols>
   <sheetData>
@@ -573,24 +564,24 @@
         <v>5</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="0" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -601,49 +592,49 @@
         <v>10</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>7</v>
@@ -651,97 +642,97 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="D9" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>1</v>
@@ -749,27 +740,27 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1</v>
@@ -777,83 +768,83 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>1</v>
@@ -861,27 +852,27 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>1</v>
@@ -889,13 +880,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>1</v>
@@ -903,52 +894,52 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>62</v>
@@ -959,27 +950,27 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>1</v>
@@ -987,27 +978,27 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>1</v>
@@ -1015,41 +1006,41 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>1</v>
@@ -1057,41 +1048,41 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>1</v>
@@ -1099,83 +1090,83 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>8</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>1</v>
@@ -1183,13 +1174,13 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>1</v>
@@ -1197,13 +1188,13 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>1</v>
@@ -1211,27 +1202,27 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>1</v>
@@ -1239,29 +1230,141 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D51" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" s="0" t="n">
         <v>1</v>
       </c>
     </row>
